--- a/reports/svod_2026/Сверка_РСВ_2026.xlsx
+++ b/reports/svod_2026/Сверка_РСВ_2026.xlsx
@@ -1067,7 +1067,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5. Уточнённый расчёт подан с КПП 366201001 в ИФНС 3662, первичный — с КПП 366301001 в ИФНС 3663: проверьте, что так и должно быть.</t>
+          <t>5. Уточнённые расчёты (1 кв. и полугодие) поданы с КПП 366201001 в ИФНС 3662, первичные — с КПП 366301001 в ИФНС 3663.</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1461,7 +1461,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>РСВ за полугодие 2026 г.: поданный расчёт и данные с учётом уточнения за 1 квартал — по сотрудникам</t>
+          <t>РСВ за полугодие 2026 г.: первичный и уточнённый — по сотрудникам</t>
         </is>
       </c>
     </row>
@@ -1475,14 +1475,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>РСВ за полугодие: корр. 0 от 24.07.2026. Уточнённого РСВ за полугодие нет — колонка «должно быть» показывает, каким он должен быть.</t>
+          <t>Первичный: корр. 0 от 24.07.2026, КПП 366301001, ИФНС 3663.   Уточнённый: корр. 3 от 15.09.2026, КПП 366201001, ИФНС 3662.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Разд. 3 РСВ за полугодие содержит только апрель–июнь; 1 кв. внутри него (разд. 1: 169 770,03 − 95 482,77 = 74 287,26 ₽) равен первичному РСВ за 1 кв., поэтому помесячно январь–март взяты из первичного РСВ за 1 кв.</t>
+          <t>Разд. 3 РСВ за полугодие содержит только апрель–июнь. Январь–март по сотрудникам взяты из РСВ за 1 кв.: для первичного п/г — из первичного 1 кв., для уточнённого п/г — из уточнённого 1 кв. (суммы 1 кв. в разд. 1 совпадают, см. контроль ниже).</t>
         </is>
       </c>
     </row>
@@ -1499,37 +1499,37 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Выплаты: РСВ п/г (подан)</t>
+          <t>Выплаты: первичный</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Выплаты: должно быть</t>
+          <t>Выплаты: уточнённый</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Разница выплат (должно быть − РСВ п/г (подан))</t>
+          <t>Разница выплат (уточнённый − первичный)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Взносы: РСВ п/г (подан)</t>
+          <t>Взносы: первичный</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Взносы: должно быть</t>
+          <t>Взносы: уточнённый</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Разница взносов (должно быть − РСВ п/г (подан))</t>
+          <t>Разница взносов (уточнённый − первичный)</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Проверка: взносы должно быть − 30% от выплат</t>
+          <t>Проверка: взносы уточнённый − 30% от выплат</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1641,110 +1641,110 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>В РСВ за полугодие остались данные первичного РСВ за 1 кв.; уточнение за 1 кв. (08.09.2026) подано позже.</t>
+          <t>Как в РСВ за 1 кв.: первичный 20 101,26, уточнённый 27 093,00.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6321.7</v>
+      </c>
+      <c r="E10" s="5">
+        <f>D10-C10</f>
+        <v/>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1896.51</v>
+      </c>
+      <c r="H10" s="5">
+        <f>G10-F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="5">
+        <f>G10-ROUND(D10*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>В первичном Лубковой в апреле нет; в уточнённом добавлено 6 321,70 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Итого Лубкова</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr"/>
-      <c r="C10" s="7">
-        <f>SUM(C7:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="7">
-        <f>SUM(D7:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="7">
-        <f>D10-C10</f>
-        <v/>
-      </c>
-      <c r="F10" s="7">
-        <f>SUM(F7:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="7">
-        <f>SUM(G7:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="7">
-        <f>G10-F10</f>
-        <v/>
-      </c>
-      <c r="I10" s="7">
-        <f>G10-ROUND(D10*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="7">
+        <f>SUM(C7:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>SUM(D7:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="7">
+        <f>D11-C11</f>
+        <v/>
+      </c>
+      <c r="F11" s="7">
+        <f>SUM(F7:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="7">
+        <f>SUM(G7:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="7">
+        <f>G11-F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="7">
+        <f>G11-ROUND(D11*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Троянова Екатерина Викторовна</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="5" t="n">
         <v>19868.2</v>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>19868.2</v>
-      </c>
-      <c r="E11" s="5">
-        <f>D11-C11</f>
-        <v/>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>5960.46</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>5960.46</v>
-      </c>
-      <c r="H11" s="5">
-        <f>G11-F11</f>
-        <v/>
-      </c>
-      <c r="I11" s="5">
-        <f>G11-ROUND(D11*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>Меньше МРОТ — проверить неполное время / неполный месяц.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Май</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>27093</v>
-      </c>
       <c r="D12" s="5" t="n">
-        <v>27093</v>
+        <v>20771.3</v>
       </c>
       <c r="E12" s="5">
         <f>D12-C12</f>
         <v/>
       </c>
       <c r="F12" s="5" t="n">
-        <v>8127.9</v>
+        <v>5960.46</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>8127.9</v>
+        <v>6231.39</v>
       </c>
       <c r="H12" s="5">
         <f>G12-F12</f>
@@ -1754,13 +1754,17 @@
         <f>G12-ROUND(D12*0.3,2)</f>
         <v/>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Увеличено на 903,10 ₽. Апрель Лубкова + Троянова в уточнённом = 27 093,00 (МРОТ).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Июнь</t>
+          <t>Май</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
@@ -1790,215 +1794,207 @@
       <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>27093</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>27093</v>
+      </c>
+      <c r="E14" s="5">
+        <f>D14-C14</f>
+        <v/>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>8127.9</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>8127.9</v>
+      </c>
+      <c r="H14" s="5">
+        <f>G14-F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="5">
+        <f>G14-ROUND(D14*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Итого Троянова</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="7">
-        <f>SUM(C11:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="7">
-        <f>SUM(D11:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="7">
-        <f>D14-C14</f>
-        <v/>
-      </c>
-      <c r="F14" s="7">
-        <f>SUM(F11:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="7">
-        <f>SUM(G11:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="7">
-        <f>G14-F14</f>
-        <v/>
-      </c>
-      <c r="I14" s="7">
-        <f>G14-ROUND(D14*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="7">
+        <f>SUM(C12:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="7">
+        <f>SUM(D12:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="7">
+        <f>D15-C15</f>
+        <v/>
+      </c>
+      <c r="F15" s="7">
+        <f>SUM(F12:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="7">
+        <f>SUM(G12:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="7">
+        <f>G15-F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="7">
+        <f>G15-ROUND(D15*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Денисова Александра Валерьевна</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="5" t="n">
         <v>21428.57</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="5" t="n">
         <v>21428.57</v>
       </c>
-      <c r="E15" s="5">
-        <f>D15-C15</f>
-        <v/>
-      </c>
-      <c r="F15" s="5" t="n">
+      <c r="E16" s="5">
+        <f>D16-C16</f>
+        <v/>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>6428.57</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>6428.57</v>
       </c>
-      <c r="H15" s="5">
-        <f>G15-F15</f>
-        <v/>
-      </c>
-      <c r="I15" s="5">
-        <f>G15-ROUND(D15*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="H16" s="5">
+        <f>G16-F16</f>
+        <v/>
+      </c>
+      <c r="I16" s="5">
+        <f>G16-ROUND(D16*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Принята в июне (30 000 × 15/21 раб. дн.).</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Итого Денисова</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr"/>
-      <c r="C16" s="7">
-        <f>SUM(C15:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="7">
-        <f>SUM(D15:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="7">
-        <f>D16-C16</f>
-        <v/>
-      </c>
-      <c r="F16" s="7">
-        <f>SUM(F15:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="7">
-        <f>SUM(G15:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="7">
-        <f>G16-F16</f>
-        <v/>
-      </c>
-      <c r="I16" s="7">
-        <f>G16-ROUND(D16*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr"/>
+      <c r="C17" s="7">
+        <f>SUM(C16:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="7">
+        <f>SUM(D16:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="7">
+        <f>D17-C17</f>
+        <v/>
+      </c>
+      <c r="F17" s="7">
+        <f>SUM(F16:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="7">
+        <f>SUM(G16:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="7">
+        <f>G17-F17</f>
+        <v/>
+      </c>
+      <c r="I17" s="7">
+        <f>G17-ROUND(D17*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Баскова Неонила Павловна</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Январь</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="5">
-        <f>D17-C17</f>
-        <v/>
-      </c>
-      <c r="F17" s="5" t="n">
+      <c r="E18" s="5">
+        <f>D18-C18</f>
+        <v/>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="5">
-        <f>G17-F17</f>
-        <v/>
-      </c>
-      <c r="I17" s="5">
-        <f>G17-ROUND(D17*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Выплат нет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Итого Баскова</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr"/>
-      <c r="C18" s="7">
-        <f>SUM(C17:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="7">
-        <f>SUM(D17:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="7">
-        <f>D18-C18</f>
-        <v/>
-      </c>
-      <c r="F18" s="7">
-        <f>SUM(F17:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="7">
-        <f>SUM(G17:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="7">
+      <c r="H18" s="5">
         <f>G18-F18</f>
         <v/>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="5">
         <f>G18-ROUND(D18*0.3,2)</f>
         <v/>
       </c>
-      <c r="J18" s="6" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Выплат нет. В уточнённом п/г в стр. 010 не учтена (3 чел. вместо 4).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ИТОГО по сотрудникам</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>п/г</t>
-        </is>
-      </c>
+          <t>Итого Баскова</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr"/>
       <c r="C19" s="7">
-        <f>C10+C14+C16+C18</f>
+        <f>SUM(C18:C18)</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>D10+D14+D16+D18</f>
+        <f>SUM(D18:D18)</f>
         <v/>
       </c>
       <c r="E19" s="7">
@@ -2006,11 +2002,11 @@
         <v/>
       </c>
       <c r="F19" s="7">
-        <f>F10+F14+F16+F18</f>
+        <f>SUM(F18:F18)</f>
         <v/>
       </c>
       <c r="G19" s="7">
-        <f>G10+G14+G16+G18</f>
+        <f>SUM(G18:G18)</f>
         <v/>
       </c>
       <c r="H19" s="7">
@@ -2024,209 +2020,213 @@
       <c r="J19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО по сотрудникам</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>п/г</t>
+        </is>
+      </c>
+      <c r="C20" s="7">
+        <f>C11+C15+C17+C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="7">
+        <f>D11+D15+D17+D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="7">
+        <f>D20-C20</f>
+        <v/>
+      </c>
+      <c r="F20" s="7">
+        <f>F11+F15+F17+F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="7">
+        <f>G11+G15+G17+G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="7">
+        <f>G20-F20</f>
+        <v/>
+      </c>
+      <c r="I20" s="7">
+        <f>G20-ROUND(D20*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Раздел 1 РСВ за полугодие (стр. 030)</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>п/г</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C21" s="9" t="n">
         <v>169770.03</v>
       </c>
-      <c r="D20" s="9" t="n">
-        <v>176761.77</v>
-      </c>
-      <c r="E20" s="9">
-        <f>D20-C20</f>
-        <v/>
-      </c>
-      <c r="F20" s="9" t="n">
+      <c r="D21" s="9" t="n">
+        <v>183986.57</v>
+      </c>
+      <c r="E21" s="9">
+        <f>D21-C21</f>
+        <v/>
+      </c>
+      <c r="F21" s="9" t="n">
         <v>50931.01</v>
       </c>
-      <c r="G20" s="9" t="n">
-        <v>53028.53</v>
-      </c>
-      <c r="H20" s="9">
-        <f>G20-F20</f>
-        <v/>
-      </c>
-      <c r="I20" s="9">
-        <f>G20-ROUND(D20*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>«Должно быть» = уточнённый 1 кв. (81 279,00 / 24 383,70) + 2 кв. (95 482,77 / 28 644,83).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="G21" s="9" t="n">
+        <v>55195.97</v>
+      </c>
+      <c r="H21" s="9">
+        <f>G21-F21</f>
+        <v/>
+      </c>
+      <c r="I21" s="9">
+        <f>G21-ROUND(D21*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Подр. 1 стр. 030 и разд. 1 стр. 030.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Контроль: раздел 1 − сумма по сотрудникам</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr"/>
-      <c r="C21" s="11">
-        <f>C20-C19</f>
-        <v/>
-      </c>
-      <c r="D21" s="11">
-        <f>D20-D19</f>
-        <v/>
-      </c>
-      <c r="E21" s="11">
-        <f>D21-C21</f>
-        <v/>
-      </c>
-      <c r="F21" s="11">
-        <f>F20-F19</f>
-        <v/>
-      </c>
-      <c r="G21" s="11">
-        <f>G20-G19</f>
-        <v/>
-      </c>
-      <c r="H21" s="11">
-        <f>G21-F21</f>
-        <v/>
-      </c>
-      <c r="I21" s="11">
-        <f>G21-ROUND(D21*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Свод по кварталам</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="62" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr"/>
+      <c r="C22" s="11">
+        <f>C21-C20</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>D21-D20</f>
+        <v/>
+      </c>
+      <c r="E22" s="11">
+        <f>D22-C22</f>
+        <v/>
+      </c>
+      <c r="F22" s="11">
+        <f>F21-F20</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>G21-G20</f>
+        <v/>
+      </c>
+      <c r="H22" s="11">
+        <f>G22-F22</f>
+        <v/>
+      </c>
+      <c r="I22" s="11">
+        <f>G22-ROUND(D22*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J22" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Свод по кварталам и месяцам</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Сотрудник</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Выплаты: РСВ п/г (подан)</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Выплаты: должно быть</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Разница выплат (должно быть − РСВ п/г (подан))</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Взносы: РСВ п/г (подан)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Взносы: должно быть</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Разница взносов (должно быть − РСВ п/г (подан))</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Проверка: взносы должно быть − 30% от выплат</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Выплаты: первичный</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Выплаты: уточнённый</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Разница выплат (уточнённый − первичный)</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Взносы: первичный</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Взносы: уточнённый</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Разница взносов (уточнённый − первичный)</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Проверка: взносы уточнённый − 30% от выплат</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>1 квартал</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>янв–мар</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>74287.25999999999</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>81279</v>
-      </c>
-      <c r="E25" s="5">
-        <f>D25-C25</f>
-        <v/>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>22286.18</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>24383.7</v>
-      </c>
-      <c r="H25" s="5">
-        <f>G25-F25</f>
-        <v/>
-      </c>
-      <c r="I25" s="5">
-        <f>G25-ROUND(D25*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Расхождение — Лубкова, март.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2 квартал</t>
+          <t>1 квартал (п/г − стр. 031–033)</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>апр–июн</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>95482.77</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>95482.77</v>
+          <t>янв–мар</t>
+        </is>
+      </c>
+      <c r="C26" s="5">
+        <f>C21-SUM(C28:C30)</f>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>D21-SUM(D28:D30)</f>
+        <v/>
       </c>
       <c r="E26" s="5">
         <f>D26-C26</f>
         <v/>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>28644.83</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>28644.83</v>
+      <c r="F26" s="5">
+        <f>F21-SUM(F28:F30)</f>
+        <v/>
+      </c>
+      <c r="G26" s="5">
+        <f>G21-SUM(G28:G30)</f>
+        <v/>
       </c>
       <c r="H26" s="5">
         <f>G26-F26</f>
@@ -2238,79 +2238,256 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
+          <t>Расхождение — Лубкова, март.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Контроль: 1 кв. в п/г − РСВ за 1 кв.</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr"/>
+      <c r="C27" s="11">
+        <f>C26-74287.26</f>
+        <v/>
+      </c>
+      <c r="D27" s="11">
+        <f>D26-81279</f>
+        <v/>
+      </c>
+      <c r="E27" s="11">
+        <f>D27-C27</f>
+        <v/>
+      </c>
+      <c r="F27" s="11">
+        <f>F26-22286.18</f>
+        <v/>
+      </c>
+      <c r="G27" s="11">
+        <f>G26-24383.7</f>
+        <v/>
+      </c>
+      <c r="H27" s="11">
+        <f>G27-F27</f>
+        <v/>
+      </c>
+      <c r="I27" s="11">
+        <f>G27-ROUND(D27*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Первичный п/г сходится с первичным 1 кв., уточнённый п/г — с уточнённым 1 кв.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>стр. 031–033</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>19868.2</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>27093</v>
+      </c>
+      <c r="E28" s="5">
+        <f>D28-C28</f>
+        <v/>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>5960.46</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>8127.9</v>
+      </c>
+      <c r="H28" s="5">
+        <f>G28-F28</f>
+        <v/>
+      </c>
+      <c r="I28" s="5">
+        <f>G28-ROUND(D28*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Расхождение: +6 321,70 Лубкова, +903,10 Троянова.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>27093</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>27093</v>
+      </c>
+      <c r="E29" s="5">
+        <f>D29-C29</f>
+        <v/>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>8127.9</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>8127.9</v>
+      </c>
+      <c r="H29" s="5">
+        <f>G29-F29</f>
+        <v/>
+      </c>
+      <c r="I29" s="5">
+        <f>G29-ROUND(D29*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
           <t>Совпадает.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>48521.57</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>48521.57</v>
+      </c>
+      <c r="E30" s="5">
+        <f>D30-C30</f>
+        <v/>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>14556.47</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>14556.47</v>
+      </c>
+      <c r="H30" s="5">
+        <f>G30-F30</f>
+        <v/>
+      </c>
+      <c r="I30" s="5">
+        <f>G30-ROUND(D30*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Совпадает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Полугодие</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr"/>
-      <c r="C27" s="7">
-        <f>C25+C26</f>
-        <v/>
-      </c>
-      <c r="D27" s="7">
-        <f>D25+D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="7">
-        <f>D27-C27</f>
-        <v/>
-      </c>
-      <c r="F27" s="7">
-        <f>F25+F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="7">
-        <f>G25+G26</f>
-        <v/>
-      </c>
-      <c r="H27" s="7">
-        <f>G27-F27</f>
-        <v/>
-      </c>
-      <c r="I27" s="7">
-        <f>G27-ROUND(D27*0.3,2)</f>
-        <v/>
-      </c>
-      <c r="J27" s="6" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr"/>
+      <c r="C31" s="7">
+        <f>SUM(C26,C28:C30)</f>
+        <v/>
+      </c>
+      <c r="D31" s="7">
+        <f>SUM(D26,D28:D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="7">
+        <f>D31-C31</f>
+        <v/>
+      </c>
+      <c r="F31" s="7">
+        <f>SUM(F26,F28:F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="7">
+        <f>SUM(G26,G28:G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="7">
+        <f>G31-F31</f>
+        <v/>
+      </c>
+      <c r="I31" s="7">
+        <f>G31-ROUND(D31*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="J31" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Вывод по полугодию:</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1. РСВ за полугодие сдан 24.07.2026 на данных первичного РСВ за 1 кв.; после уточнения 1 кв. (08.09.2026) он с ним не сходится.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2. Расхождение: выплаты 6 991,74 ₽, взносы 2 097,52 ₽ — Лубкова Н.И., март. Апрель–июнь (Троянова, Денисова) сходятся.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>3. Нужен уточнённый РСВ за полугодие: стр. 030 разд. 1 — 53 028,53 ₽ вместо 50 931,01 ₽; подр. 1 стр. 030/050 — 176 761,77 ₽ вместо 169 770,03 ₽. Строки 031–033 и разд. 3 (апрель–июнь) не меняются.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>4. Иначе ФНС увидит несоответствие нарастающего итога (1 кв. в РСВ за полугодие ≠ уточнённому РСВ за 1 кв.) и пришлёт требование.</t>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1. Уточнённый РСВ за полугодие больше первичного на 14 216,54 ₽ выплат и 4 264,96 ₽ взносов:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Лубкова, март: +6 991,74 ₽ / +2 097,52 ₽ (то же, что в уточнённом РСВ за 1 кв.);</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Лубкова, апрель: +6 321,70 ₽ / +1 896,51 ₽ (в первичном не было);</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Троянова, апрель: +903,10 ₽ / +270,93 ₽ (20 771,30 вместо 19 868,20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2. Май, июнь, Денисова — без изменений. Взносы везде = 30% от выплат.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3. Уточнённый РСВ за полугодие сходится с уточнённым РСВ за 1 кв. (1 кв. = 81 279,00 / 24 383,70).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4. Доплата взносов: за март 2 097,52 ₽ (срок 28.04.2026), за апрель 2 167,44 ₽ (срок 28.05.2026) — на них начисляются пени.</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2942,7 @@
       <formula>0.005</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E25">
+  <conditionalFormatting sqref="E22">
     <cfRule type="cellIs" priority="91" operator="notBetween" dxfId="0">
       <formula>-0.005</formula>
       <formula>0.005</formula>
@@ -2775,7 +2952,7 @@
       <formula>0.005</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
+  <conditionalFormatting sqref="H22">
     <cfRule type="cellIs" priority="93" operator="notBetween" dxfId="0">
       <formula>-0.005</formula>
       <formula>0.005</formula>
@@ -2785,7 +2962,7 @@
       <formula>0.005</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I25">
+  <conditionalFormatting sqref="I22">
     <cfRule type="cellIs" priority="95" operator="notBetween" dxfId="0">
       <formula>-0.005</formula>
       <formula>0.005</formula>
@@ -2851,6 +3028,126 @@
       <formula>0.005</formula>
     </cfRule>
     <cfRule type="cellIs" priority="108" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28">
+    <cfRule type="cellIs" priority="109" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="110" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="cellIs" priority="111" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="112" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28">
+    <cfRule type="cellIs" priority="113" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="114" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="cellIs" priority="115" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="116" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="cellIs" priority="117" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="118" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
+    <cfRule type="cellIs" priority="119" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="120" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30">
+    <cfRule type="cellIs" priority="121" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="122" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="cellIs" priority="123" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="124" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30">
+    <cfRule type="cellIs" priority="125" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="126" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31">
+    <cfRule type="cellIs" priority="127" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="128" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="cellIs" priority="129" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="130" operator="between" dxfId="1">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I31">
+    <cfRule type="cellIs" priority="131" operator="notBetween" dxfId="0">
+      <formula>-0.005</formula>
+      <formula>0.005</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="132" operator="between" dxfId="1">
       <formula>-0.005</formula>
       <formula>0.005</formula>
     </cfRule>
